--- a/results/tab03.xlsx
+++ b/results/tab03.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:K10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -434,25 +434,35 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
+          <t>H3(OLS)+geo+country+region</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
           <t>H3(RLM)+full</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>H3(RLM)+geo</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>H3(RLM)+geo+country</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>H3(RLM)+geo+country+region</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
         <is>
           <t>H3(MLM)+geo+country</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>H3(MLM)+geo+country+region</t>
         </is>
@@ -484,29 +494,41 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
+          <t>4.650***
+[4.529, 4.771]</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
           <t>3.872***
 [3.819, 3.925]</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>4.442***
 [4.326, 4.558]</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>4.466***
 [4.348, 4.584]</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>4.553***
+[4.433, 4.673]</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
         <is>
           <t>4.458***
 [4.334, 4.582]</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>4.448***
 [4.327, 4.569]</t>
@@ -539,29 +561,41 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
+          <t>0.073**
+[0.030, 0.116]</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
           <t>-0.075***
 [-0.101, -0.050]</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>0.045*
 [0.001, 0.088]</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>0.045*
 [0.001, 0.088]</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>0.041⁺
+[-0.002, 0.084]</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
         <is>
           <t>0.059**
 [0.016, 0.102]</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>0.056*
 [0.013, 0.099]</t>
@@ -594,29 +628,41 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
+          <t>1.775***
+[1.661, 1.890]</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
           <t>2.355***
 [2.293, 2.417]</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>1.881***
 [1.767, 1.995]</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>1.880***
 [1.766, 1.994]</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1.868***
+[1.755, 1.982]</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
         <is>
           <t>1.800***
 [1.686, 1.913]</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>1.771***
 [1.658, 1.883]</t>
@@ -649,29 +695,41 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
+          <t>-0.210***
+[-0.255, -0.164]</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
           <t>-0.026*
 [-0.049, -0.003]</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>-0.184***
 [-0.230, -0.139]</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>-0.184***
 [-0.229, -0.139]</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>-0.171***
+[-0.217, -0.126]</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
         <is>
           <t>-0.188***
 [-0.233, -0.142]</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>-0.172***
 [-0.217, -0.127]</t>
@@ -692,46 +750,60 @@
 [-0.001, -0.000]</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>-0.000*
+[-0.001, -0.000]</t>
+        </is>
+      </c>
       <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr">
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
         <is>
           <t>-0.001*
 [-0.001, -0.000]</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>-0.000⁺
+[-0.001, 0.000]</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Country Var.</t>
+          <t>Region</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>-0.000***
+[-0.000, -0.000]</t>
+        </is>
+      </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>0.017
-(0.009)</t>
-        </is>
-      </c>
+      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0.006
-(0.008)</t>
-        </is>
-      </c>
+          <t>-0.000***
+[-0.000, -0.000]</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Region Var.</t>
+          <t>Country Var.</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -741,9 +813,16 @@
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>0.019
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>0.017
+(0.009)</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0.006
 (0.008)</t>
         </is>
       </c>
@@ -751,46 +830,78 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>Region Var.</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>0.019
+(0.008)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>Model</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>R² = .68, R²adj = .68, F(3, 35478) = 25685.95, p &lt; .0001, AIC = 66336.3, BIC = 66370.2, LL = -33164.1, MAE = 0.492, MAD = 0.473, N = 35481</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>R² = .74, R²adj = .74, F(3, 7914) = 7432.64, p &lt; .0001, AIC = 15026.6, BIC = 15054.5, LL = -7509.3, MAE = 0.490, MAD = 0.414, N = 7917</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>R² = .74, R²adj = .74, F(4, 7913) = 5578.52, p &lt; .0001, AIC = 15023.6, BIC = 15058.5, LL = -7506.8, MAE = 0.490, MAD = 0.417, N = 7917</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>R² = .74, R²adj = .74, F(5, 7912) = 4498.27, p &lt; .0001, AIC = 14978.6, BIC = 15020.4, LL = -7483.3, MAE = 0.483, MAD = 0.416, N = 7917</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
         <is>
           <t>R² = .70, R²adj = .70, F(3, 35478) = 27342.90, p &lt; .0001, MAE = 0.492, MAD = 0.477, N = 35481</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>R² = .75, R²adj = .75, F(3, 7914) = 8122.46, p &lt; .0001, MAE = 0.489, MAD = 0.422, N = 7917</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>R² = .76, R²adj = .76, F(4, 7913) = 6104.72, p &lt; .0001, MAE = 0.489, MAD = 0.421, N = 7917</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>R² = .76, R²adj = .76, F(5, 7912) = 4924.96, p &lt; .0001, MAE = 0.483, MAD = 0.423, N = 7917</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
         <is>
           <t>R² = .74, R²adj = .74, F(3, 7914) = 7584.52, p &lt; .0001, AIC = 14844.7, BIC = 14886.6, LL = -7416.4, MAE = 0.473, MAD = 0.381, N = 7917, G = 97,
  ICC = 0.04, LRTstat. = 51495.5 (p &lt; .0001)</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>R² = .74, R²adj = .74, F(3, 7914) = 7587.55, p &lt; .0001, AIC = 14712.9, BIC = 14761.7, LL = -7349.5, MAE = 0.457, MAD = 0.362, N = 7917, G = 97,
  ICC = 0.02, LRTstat. = 51495.5 (p &lt; .0001)</t>

--- a/results/tab03.xlsx
+++ b/results/tab03.xlsx
@@ -476,8 +476,8 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>3.933***
-[3.879, 3.986]</t>
+          <t>3.881***
+[3.817, 3.946]</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -500,8 +500,8 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>3.872***
-[3.819, 3.925]</t>
+          <t>3.838***
+[3.774, 3.901]</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -543,8 +543,8 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>-0.058***
-[-0.084, -0.033]</t>
+          <t>-0.035*
+[-0.069, -0.002]</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -567,8 +567,8 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-0.075***
-[-0.101, -0.050]</t>
+          <t>-0.046**
+[-0.079, -0.013]</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -610,8 +610,8 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2.298***
-[2.235, 2.361]</t>
+          <t>2.336***
+[2.257, 2.416]</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -634,8 +634,8 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2.355***
-[2.293, 2.417]</t>
+          <t>2.372***
+[2.293, 2.450]</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -677,8 +677,8 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>-0.046***
-[-0.069, -0.023]</t>
+          <t>-0.056***
+[-0.085, -0.028]</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -701,8 +701,8 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-0.026*
-[-0.049, -0.003]</t>
+          <t>-0.042**
+[-0.070, -0.014]</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>R² = .68, R²adj = .68, F(3, 35478) = 25685.95, p &lt; .0001, AIC = 66336.3, BIC = 66370.2, LL = -33164.1, MAE = 0.492, MAD = 0.473, N = 35481</t>
+          <t>R² = .66, R²adj = .66, F(3, 27561) = 17807.95, p &lt; .0001, AIC = 50965.6, BIC = 50998.5, LL = -25478.8, MAE = 0.490, MAD = 0.492, N = 27564</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -877,7 +877,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>R² = .70, R²adj = .70, F(3, 35478) = 27342.90, p &lt; .0001, MAE = 0.492, MAD = 0.477, N = 35481</t>
+          <t>R² = .67, R²adj = .67, F(3, 27561) = 18878.82, p &lt; .0001, MAE = 0.489, MAD = 0.493, N = 27564</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">

--- a/results/tab03.xlsx
+++ b/results/tab03.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="B1" t="inlineStr">
         <is>
-          <t>H3(OLS)+full</t>
+          <t>H3(OLS)+nogeo</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
@@ -439,7 +439,7 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>H3(RLM)+full</t>
+          <t>H3(RLM)+nogeo</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
